--- a/artfynd/A 27226-2026 artfynd.xlsx
+++ b/artfynd/A 27226-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130339304</v>
+        <v>130408470</v>
       </c>
       <c r="B2" t="n">
-        <v>58236</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483441</v>
+        <v>483517</v>
       </c>
       <c r="R2" t="n">
-        <v>6331686</v>
+        <v>6331625</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -780,48 +776,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130408470</v>
+        <v>130339302</v>
       </c>
       <c r="B3" t="n">
-        <v>91798</v>
+        <v>96350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>2813</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skogslund, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483517</v>
+        <v>483334</v>
       </c>
       <c r="R3" t="n">
-        <v>6331625</v>
+        <v>6331500</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +855,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -881,10 +873,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131584750</v>
+        <v>130331339</v>
       </c>
       <c r="B4" t="n">
-        <v>58073</v>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -892,21 +884,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -914,27 +906,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skogslund, 400 m. NNV., Sm</t>
+          <t>Skogslund 450 m. NV, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483533</v>
+        <v>483367</v>
       </c>
       <c r="R4" t="n">
-        <v>6331587</v>
+        <v>6331698</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -958,27 +949,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>I äldre, flerskiktad barrskog.</t>
+          <t>På gammal tall i gran- tallskog. På en meters höjd.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -987,6 +968,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -998,10 +980,353 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
+          <t>Uno Pettersson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130330460</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skogslund 400 m. NV, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>483323</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6331555</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Asa</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Kärrkant i äldre barrskog. Minst en bål.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Uno Pettersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Uno Pettersson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130339304</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skogslund, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>483441</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6331686</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Asa</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Uno Pettersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131584750</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skogslund, 400 m. NNV., Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>483533</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6331587</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Asa</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>I äldre, flerskiktad barrskog.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Uno Pettersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
           <t>Uno Pettersson, Per Fogelström</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27226-2026 artfynd.xlsx
+++ b/artfynd/A 27226-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -776,48 +776,59 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130339302</v>
+        <v>135313518</v>
       </c>
       <c r="B3" t="n">
-        <v>96350</v>
+        <v>91974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2813</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skogslund, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483334</v>
+        <v>483525</v>
       </c>
       <c r="R3" t="n">
-        <v>6331500</v>
+        <v>6331610</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -841,12 +852,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -855,77 +866,87 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Barrskog. Fuktstråk med liten bäck/skogsdike</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>låga # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Per Fogelström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Uno Pettersson</t>
+          <t>Per Fogelström, Uno Pettersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130331339</v>
+        <v>130339302</v>
       </c>
       <c r="B4" t="n">
-        <v>91930</v>
+        <v>96350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>2813</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skogslund 450 m. NV, Sm</t>
+          <t>Skogslund, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483367</v>
+        <v>483334</v>
       </c>
       <c r="R4" t="n">
-        <v>6331698</v>
+        <v>6331500</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -957,62 +978,56 @@
           <t>2025-12-28</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På gammal tall i gran- tallskog. På en meters höjd.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Uno Pettersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Uno Pettersson, Elin Kannerby</t>
+          <t>Elin Kannerby, Uno Pettersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130330460</v>
+        <v>130331339</v>
       </c>
       <c r="B5" t="n">
-        <v>79327</v>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1022,21 +1037,21 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skogslund 400 m. NV, Sm</t>
+          <t>Skogslund 450 m. NV, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483323</v>
+        <v>483367</v>
       </c>
       <c r="R5" t="n">
-        <v>6331555</v>
+        <v>6331698</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1073,7 +1088,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Kärrkant i äldre barrskog. Minst en bål.</t>
+          <t>På gammal tall i gran- tallskog. På en meters höjd.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,56 +1116,59 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130339304</v>
+        <v>130330460</v>
       </c>
       <c r="B6" t="n">
-        <v>58327</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skogslund, Sm</t>
+          <t>Skogslund 400 m. NV, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483441</v>
+        <v>483323</v>
       </c>
       <c r="R6" t="n">
-        <v>6331686</v>
+        <v>6331555</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1182,84 +1200,86 @@
           <t>2025-12-28</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Kärrkant i äldre barrskog. Minst en bål.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Uno Pettersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Uno Pettersson</t>
+          <t>Uno Pettersson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131584750</v>
+        <v>130339304</v>
       </c>
       <c r="B7" t="n">
-        <v>58136</v>
+        <v>58327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skogslund, 400 m. NNV., Sm</t>
+          <t>Skogslund, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483533</v>
+        <v>483441</v>
       </c>
       <c r="R7" t="n">
-        <v>6331587</v>
+        <v>6331686</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1283,27 +1303,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>I äldre, flerskiktad barrskog.</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1318,15 +1323,139 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Uno Pettersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131584750</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skogslund, 400 m. NNV., Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>483533</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6331587</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Asa</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>I äldre, flerskiktad barrskog.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Uno Pettersson</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Uno Pettersson, Per Fogelström</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27226-2026 artfynd.xlsx
+++ b/artfynd/A 27226-2026 artfynd.xlsx
@@ -898,7 +898,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Per Fogelström, Uno Pettersson</t>
+          <t>Uno Pettersson, Per Fogelström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 27226-2026 artfynd.xlsx
+++ b/artfynd/A 27226-2026 artfynd.xlsx
@@ -898,7 +898,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Uno Pettersson, Per Fogelström</t>
+          <t>Per Fogelström, Uno Pettersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 27226-2026 artfynd.xlsx
+++ b/artfynd/A 27226-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130408470</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135313518</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -999,6 +1014,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130339302</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1113,6 +1133,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130331339</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130330460</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1332,6 +1362,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130339304</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1456,8 +1491,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131584750</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 27226-2026 artfynd.xlsx
+++ b/artfynd/A 27226-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>135313518</v>
       </c>
       <c r="B3" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27226-2026 artfynd.xlsx
+++ b/artfynd/A 27226-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>135313518</v>
       </c>
       <c r="B3" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27226-2026 artfynd.xlsx
+++ b/artfynd/A 27226-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,48 +786,59 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130339302</v>
+        <v>135313518</v>
       </c>
       <c r="B3" t="n">
-        <v>96350</v>
+        <v>92048</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2813</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skogslund, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483334</v>
+        <v>483525</v>
       </c>
       <c r="R3" t="n">
-        <v>6331500</v>
+        <v>6331610</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,12 +862,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -865,82 +876,92 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Barrskog. Fuktstråk med liten bäck/skogsdike</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>låga # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Per Fogelström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Uno Pettersson</t>
+          <t>Per Fogelström, Uno Pettersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130339302</t>
+          <t>https://artportalen.se/Sighting/135313518</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130331339</v>
+        <v>130339302</v>
       </c>
       <c r="B4" t="n">
-        <v>91930</v>
+        <v>96350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>2813</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skogslund 450 m. NV, Sm</t>
+          <t>Skogslund, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483367</v>
+        <v>483334</v>
       </c>
       <c r="R4" t="n">
-        <v>6331698</v>
+        <v>6331500</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,67 +993,61 @@
           <t>2025-12-28</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På gammal tall i gran- tallskog. På en meters höjd.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Uno Pettersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Uno Pettersson, Elin Kannerby</t>
+          <t>Elin Kannerby, Uno Pettersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130331339</t>
+          <t>https://artportalen.se/Sighting/130339302</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130330460</v>
+        <v>130331339</v>
       </c>
       <c r="B5" t="n">
-        <v>79327</v>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1042,21 +1057,21 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skogslund 400 m. NV, Sm</t>
+          <t>Skogslund 450 m. NV, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483323</v>
+        <v>483367</v>
       </c>
       <c r="R5" t="n">
-        <v>6331555</v>
+        <v>6331698</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1093,7 +1108,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Kärrkant i äldre barrskog. Minst en bål.</t>
+          <t>På gammal tall i gran- tallskog. På en meters höjd.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,62 +1135,65 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130330460</t>
+          <t>https://artportalen.se/Sighting/130331339</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130339304</v>
+        <v>130330460</v>
       </c>
       <c r="B6" t="n">
-        <v>58327</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skogslund, Sm</t>
+          <t>Skogslund 400 m. NV, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483441</v>
+        <v>483323</v>
       </c>
       <c r="R6" t="n">
-        <v>6331686</v>
+        <v>6331555</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1207,89 +1225,91 @@
           <t>2025-12-28</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Kärrkant i äldre barrskog. Minst en bål.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Uno Pettersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Uno Pettersson</t>
+          <t>Uno Pettersson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130339304</t>
+          <t>https://artportalen.se/Sighting/130330460</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131584750</v>
+        <v>130339304</v>
       </c>
       <c r="B7" t="n">
-        <v>58136</v>
+        <v>58327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skogslund, 400 m. NNV., Sm</t>
+          <t>Skogslund, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483533</v>
+        <v>483441</v>
       </c>
       <c r="R7" t="n">
-        <v>6331587</v>
+        <v>6331686</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1313,27 +1333,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>I äldre, flerskiktad barrskog.</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,16 +1353,145 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Uno Pettersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Uno Pettersson, Per Fogelström</t>
+          <t>Elin Kannerby, Uno Pettersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130339304</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131584750</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skogslund, 400 m. NNV., Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>483533</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6331587</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Asa</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>I äldre, flerskiktad barrskog.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Uno Pettersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Uno Pettersson, Per Fogelström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/131584750</t>
         </is>
@@ -1371,6 +1505,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27226-2026 artfynd.xlsx
+++ b/artfynd/A 27226-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>135313518</v>
       </c>
       <c r="B3" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
